--- a/Systeme electric/Сезонность SystemElectric 2024-2026.xlsx
+++ b/Systeme electric/Сезонность SystemElectric 2024-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.13\од\Кейсы для Хакатона\Systeme electric\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\githack\hack-95b86b43-team\Systeme electric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF5EB98-C11F-4F9B-BD57-F838C8315C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E7CEFE-84D2-41EF-94E1-46E0630B453D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C20A6AEE-0A31-41C9-B10A-E7030CB8D491}"/>
+    <workbookView xWindow="1044" yWindow="1044" windowWidth="17280" windowHeight="10500" xr2:uid="{C20A6AEE-0A31-41C9-B10A-E7030CB8D491}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -252,7 +249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -290,6 +287,9 @@
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -309,9 +309,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -349,7 +349,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -455,7 +455,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -597,7 +597,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -628,26 +628,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4D582D-AC88-44B0-8CEA-0F362673C55C}">
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="22.1640625" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="13" max="13" width="19.5" customWidth="1"/>
-    <col min="14" max="14" width="21.83203125" customWidth="1"/>
-    <col min="15" max="15" width="44.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" customWidth="1"/>
+    <col min="14" max="14" width="21.85546875" customWidth="1"/>
+    <col min="15" max="15" width="44.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -664,7 +664,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -681,7 +681,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +726,7 @@
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2024</v>
       </c>
@@ -745,22 +745,22 @@
       <c r="F4" s="3">
         <v>73462110</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="15">
         <v>68345412</v>
       </c>
       <c r="H4" s="3">
         <v>71289315.980000004</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="15">
         <v>91399515.640000001</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="15">
         <v>99082123</v>
       </c>
       <c r="K4" s="3">
         <v>88432469</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="15">
         <v>82883679</v>
       </c>
       <c r="M4" s="3">
@@ -772,7 +772,7 @@
       </c>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2025</v>
       </c>
@@ -791,22 +791,22 @@
       <c r="F5" s="3">
         <v>77227054</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="15">
         <v>80386586</v>
       </c>
       <c r="H5" s="3">
         <v>79580845.349999994</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="15">
         <v>85147826.950000003</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="15">
         <v>75393744</v>
       </c>
       <c r="K5" s="3">
         <v>70827551</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="15">
         <v>72949510</v>
       </c>
       <c r="M5" s="3">
@@ -818,7 +818,7 @@
       </c>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2026</v>
       </c>
@@ -837,16 +837,16 @@
       <c r="F6" s="3">
         <v>59215517</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="15">
         <v>68110627</v>
       </c>
       <c r="H6" s="3">
         <v>72110849.170000002</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="15">
         <v>70105174.180000007</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="15">
         <v>45371784.460000001</v>
       </c>
       <c r="K6" s="1"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -875,7 +875,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
     </row>
-    <row r="8" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>14</v>
@@ -894,7 +894,7 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
     </row>
-    <row r="9" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -911,7 +911,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
     </row>
-    <row r="10" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
         <v>15</v>
@@ -956,7 +956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="str" cm="1">
         <f t="array" ref="B11">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -999,7 +999,7 @@
         <v>9.6253230770666873E-2</v>
       </c>
       <c r="L11" s="14">
-        <f>AVERAGE(G11,J11)</f>
+        <f t="shared" ref="L11:L19" si="0">AVERAGE(G11,J11)</f>
         <v>0.84316910263515044</v>
       </c>
       <c r="M11" s="8">
@@ -1015,7 +1015,7 @@
         <v>794192664.94000006</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="str" cm="1">
         <f t="array" ref="B12">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1026,11 +1026,11 @@
         <v>22395512</v>
       </c>
       <c r="D12" s="6">
-        <f t="shared" ref="D12:D22" si="0">IFERROR(C12/$N$11,"")</f>
+        <f t="shared" ref="D12:D22" si="1">IFERROR(C12/$N$11,"")</f>
         <v>0.33838910363180363</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" ref="E12:E22" si="1">IFERROR(C12/$O$11,"")</f>
+        <f t="shared" ref="E12:E22" si="2">IFERROR(C12/$O$11,"")</f>
         <v>2.8199091969316973E-2</v>
       </c>
       <c r="F12" s="5" cm="1">
@@ -1038,11 +1038,11 @@
         <v>70526214</v>
       </c>
       <c r="G12" s="6">
-        <f t="shared" ref="G12:G22" si="2">IFERROR(F12/$N$12,"")</f>
+        <f t="shared" ref="G12:G22" si="3">IFERROR(F12/$N$12,"")</f>
         <v>0.9541914918042389</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" ref="H12:H22" si="3">IFERROR(F12/$O$12,"")</f>
+        <f t="shared" ref="H12:H22" si="4">IFERROR(F12/$O$12,"")</f>
         <v>7.9515957650353242E-2</v>
       </c>
       <c r="I12" s="5" cm="1">
@@ -1050,15 +1050,15 @@
         <v>57127585</v>
       </c>
       <c r="J12" s="6">
-        <f t="shared" ref="J12:J22" si="4">IFERROR(I12/$N$13,"")</f>
+        <f t="shared" ref="J12:J22" si="5">IFERROR(I12/$N$13,"")</f>
         <v>0.96162378852029617</v>
       </c>
       <c r="K12" s="7">
-        <f t="shared" ref="K12:K22" si="5">IFERROR(I12/$O$13,"")</f>
+        <f t="shared" ref="K12:K22" si="6">IFERROR(I12/$O$13,"")</f>
         <v>0.10684708761336624</v>
       </c>
       <c r="L12" s="14">
-        <f>AVERAGE(G12,J12)</f>
+        <f t="shared" si="0"/>
         <v>0.95790764016226748</v>
       </c>
       <c r="M12" s="8">
@@ -1074,7 +1074,7 @@
         <v>886944156.67000008</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="str" cm="1">
         <f t="array" ref="B13">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1085,11 +1085,11 @@
         <v>44147660</v>
       </c>
       <c r="D13" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.66705718069056119</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.5588098390880109E-2</v>
       </c>
       <c r="F13" s="5" cm="1">
@@ -1097,11 +1097,11 @@
         <v>62394638.899999999</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.84417453023322364</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.0347877519435303E-2</v>
       </c>
       <c r="I13" s="5" cm="1">
@@ -1109,15 +1109,15 @@
         <v>49906664.43</v>
       </c>
       <c r="J13" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.84007464557774858</v>
       </c>
       <c r="K13" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.3341627286416512E-2</v>
       </c>
       <c r="L13" s="14">
-        <f>AVERAGE(G13,J13)</f>
+        <f t="shared" si="0"/>
         <v>0.84212458790548617</v>
       </c>
       <c r="M13" s="8">
@@ -1133,7 +1133,7 @@
         <v>534666749.24000001</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="str" cm="1">
         <f t="array" ref="B14">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1144,11 +1144,11 @@
         <v>62276496.32</v>
       </c>
       <c r="D14" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.94097816415423408</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.841484701285284E-2</v>
       </c>
       <c r="F14" s="5" cm="1">
@@ -1156,11 +1156,11 @@
         <v>80289436.030000001</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0862839843010248</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0523665358418728E-2</v>
       </c>
       <c r="I14" s="5" cm="1">
@@ -1168,22 +1168,22 @@
         <v>61255146</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0311026724284575</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11456696360316196</v>
       </c>
       <c r="L14" s="14">
-        <f>AVERAGE(G14,J14)</f>
+        <f t="shared" si="0"/>
         <v>1.0586933283647411</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="str" cm="1">
         <f t="array" ref="B15">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1194,11 +1194,11 @@
         <v>73462110</v>
       </c>
       <c r="D15" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1099892493550028</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.2499104112916911E-2</v>
       </c>
       <c r="F15" s="5" cm="1">
@@ -1206,11 +1206,11 @@
         <v>77227054</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0448511792211974</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.7070931601766446E-2</v>
       </c>
       <c r="I15" s="5" cm="1">
@@ -1218,15 +1218,15 @@
         <v>59215517</v>
       </c>
       <c r="J15" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.99676977062356131</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.11075219673595126</v>
       </c>
       <c r="L15" s="14">
-        <f>AVERAGE(G15,J15)</f>
+        <f t="shared" si="0"/>
         <v>1.0208104749223794</v>
       </c>
       <c r="M15" s="1" t="s">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="str" cm="1">
         <f t="array" ref="B16">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1249,11 +1249,11 @@
         <v>68345412</v>
       </c>
       <c r="D16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0326775607553118</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6056463396275998E-2</v>
       </c>
       <c r="F16" s="5" cm="1">
@@ -1261,11 +1261,11 @@
         <v>80386586</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.08759838457215</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.0633198714345831E-2</v>
       </c>
       <c r="I16" s="5" cm="1">
@@ -1273,22 +1273,22 @@
         <v>68110627</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1465004021127931</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.12738893356808814</v>
       </c>
       <c r="L16" s="14">
-        <f>AVERAGE(G16,J16)</f>
+        <f t="shared" si="0"/>
         <v>1.1170493933424717</v>
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="str" cm="1">
         <f t="array" ref="B17">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1299,11 +1299,11 @@
         <v>71289315.980000004</v>
       </c>
       <c r="D17" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.0771590188693438</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.9763251572445329E-2</v>
       </c>
       <c r="F17" s="5" cm="1">
@@ -1311,11 +1311,11 @@
         <v>79580845.349999994</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0766970355669301</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.9724752963910845E-2</v>
       </c>
       <c r="I17" s="5" cm="1">
@@ -1323,22 +1323,22 @@
         <v>72110849.170000002</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2138358023058573</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.1348706447006508</v>
       </c>
       <c r="L17" s="14">
-        <f>AVERAGE(G17,J17)</f>
+        <f t="shared" si="0"/>
         <v>1.1452664189363937</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="str" cm="1">
         <f t="array" ref="B18">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1349,11 +1349,11 @@
         <v>91399515.640000001</v>
       </c>
       <c r="D18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3810177757847473</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11508481464872895</v>
       </c>
       <c r="F18" s="5" cm="1">
@@ -1361,11 +1361,11 @@
         <v>85147826.950000003</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1520160719432591</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.6001339328604926E-2</v>
       </c>
       <c r="I18" s="5" cm="1">
@@ -1373,22 +1373,22 @@
         <v>70105174.180000007</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1800744454688021</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.1311193828298669</v>
       </c>
       <c r="L18" s="14">
-        <f>AVERAGE(G18,J18)</f>
+        <f t="shared" si="0"/>
         <v>1.1660452587060306</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="str" cm="1">
         <f t="array" ref="B19">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1399,11 +1399,11 @@
         <v>99082123</v>
       </c>
       <c r="D19" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.4970995433328838</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12475829527774031</v>
       </c>
       <c r="F19" s="5" cm="1">
@@ -1411,11 +1411,11 @@
         <v>75393744</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.0200472275467232</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.5003935628893593E-2</v>
       </c>
       <c r="I19" s="5" cm="1">
@@ -1423,22 +1423,22 @@
         <v>45371784.460000001</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.76373939602648178</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.4859932891831316E-2</v>
       </c>
       <c r="L19" s="14">
-        <f>AVERAGE(G19,J19)</f>
+        <f t="shared" si="0"/>
         <v>0.89189331178660247</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
     </row>
-    <row r="20" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="str" cm="1">
         <f t="array" ref="B20">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1449,11 +1449,11 @@
         <v>88432469</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.3361866393970927</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.11134888661642441</v>
       </c>
       <c r="F20" s="5" cm="1">
@@ -1461,11 +1461,11 @@
         <v>70827551</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.95826846099424556</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.9855705082853792E-2</v>
       </c>
       <c r="I20" s="5" cm="1">
@@ -1473,11 +1473,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L20" s="14">
@@ -1488,7 +1488,7 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
     </row>
-    <row r="21" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="str" cm="1">
         <f t="array" ref="B21">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1499,11 +1499,11 @@
         <v>82883679</v>
       </c>
       <c r="D21" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2523461773285713</v>
       </c>
       <c r="E21" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.10436218144404762</v>
       </c>
       <c r="F21" s="5" cm="1">
@@ -1511,11 +1511,11 @@
         <v>72949510</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.98697771828909242</v>
       </c>
       <c r="H21" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.2248143190757697E-2</v>
       </c>
       <c r="I21" s="5" cm="1">
@@ -1523,11 +1523,11 @@
         <v>0</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K21" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L21" s="14">
@@ -1538,7 +1538,7 @@
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
     </row>
-    <row r="22" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="str" cm="1">
         <f t="array" ref="B22">INDEX($B$3:$M$3,ROW()-10)</f>
@@ -1549,11 +1549,11 @@
         <v>65881945</v>
       </c>
       <c r="D22" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.99545535346857839</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.2954612789048199E-2</v>
       </c>
       <c r="F22" s="5" cm="1">
@@ -1561,11 +1561,11 @@
         <v>71608529.439999998</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.96883478719361515</v>
       </c>
       <c r="H22" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.0736232266134592E-2</v>
       </c>
       <c r="I22" s="5" cm="1">
@@ -1573,11 +1573,11 @@
         <v>0</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L22" s="14">
@@ -1588,7 +1588,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>28</v>
@@ -1637,7 +1637,7 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1654,7 +1654,7 @@
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
     </row>
-    <row r="25" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1671,7 +1671,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1688,7 +1688,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1705,7 +1705,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1722,7 +1722,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1739,7 +1739,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1756,7 +1756,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1773,7 +1773,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1790,7 +1790,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1807,7 +1807,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1824,7 +1824,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
